--- a/MAJSushiConfig/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-diagnostic-report-imaging-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-diagnostic-report-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-diagnostic-report-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-document|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -466,7 +466,7 @@
     <t>comparaison</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-comparison-studies-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-comparison-studies-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>historiqueMedical</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-history-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-history-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -499,7 +499,7 @@
     <t>procedure</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-imaging-procedure-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-procedure-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -609,7 +609,7 @@
     <t>serviceRequestAccessionNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-service-request-imaging-document|0.1.0)
 </t>
   </si>
   <si>
@@ -725,7 +725,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0)
 </t>
   </si>
   <si>
@@ -856,7 +856,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitioner-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitioner-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -890,7 +890,7 @@
     <t>organization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0)
 </t>
   </si>
   <si>
@@ -950,7 +950,7 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1026,7 +1026,7 @@
     <t>AUT</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1071,7 +1071,7 @@
     <t>DiagnosticReport.resultsInterpreter.extension:author.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1081,7 +1081,7 @@
     <t>DiagnosticReport.resultsInterpreter.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter.extension:author.value[x]</t>
@@ -1203,7 +1203,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-result-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-laboratory-report-results-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-result-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-laboratory-report-results-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1235,7 +1235,7 @@
     <t>resultatActuel</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-result-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-result-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1257,7 +1257,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-imaging-study-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-imaging-study-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-media-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-media-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1766,7 +1766,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
